--- a/Data/FlightPlan/FPL_28OCT26.xlsx
+++ b/Data/FlightPlan/FPL_28OCT26.xlsx
@@ -203,6 +203,9 @@
     <t>04:05</t>
   </si>
   <si>
+    <t>08:08</t>
+  </si>
+  <si>
     <t>10:35</t>
   </si>
   <si>
@@ -371,6 +374,12 @@
     <t>14:20</t>
   </si>
   <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
     <t>15:50</t>
   </si>
   <si>
@@ -440,6 +449,9 @@
     <t>19:25</t>
   </si>
   <si>
+    <t>12:20</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -545,18 +557,12 @@
     <t>09:05</t>
   </si>
   <si>
-    <t>11:15</t>
-  </si>
-  <si>
     <t>12:55</t>
   </si>
   <si>
     <t>VDH</t>
   </si>
   <si>
-    <t>14:45</t>
-  </si>
-  <si>
     <t>16:20</t>
   </si>
   <si>
@@ -785,9 +791,6 @@
     <t>VN-A633</t>
   </si>
   <si>
-    <t>12:20</t>
-  </si>
-  <si>
     <t>19:45</t>
   </si>
   <si>
@@ -1163,7 +1166,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 27, 2026 21:51</t>
+    <t xml:space="preserve">Generated on  Oct 28, 2026 02:54</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2329,7 +2332,9 @@
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
+      <c t="s" r="M26" s="7">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c t="s" r="A27" s="6">
@@ -2358,7 +2363,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2385,13 +2390,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H28" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2415,7 +2420,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H29" s="8">
         <v>17</v>
@@ -2424,7 +2429,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2451,10 +2456,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J30" s="7">
         <v>30</v>
@@ -2481,16 +2486,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2523,13 +2528,13 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H33" s="8">
         <v>17</v>
@@ -2538,7 +2543,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2571,7 +2576,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2604,7 +2609,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2619,7 +2624,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2652,7 +2657,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2670,7 +2675,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2679,13 +2684,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2703,22 +2708,22 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="H39" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2736,7 +2741,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2745,10 +2750,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J40" s="7">
         <v>33</v>
@@ -2784,22 +2789,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2817,7 +2822,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2826,13 +2831,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2850,22 +2855,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2883,7 +2888,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2895,10 +2900,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2931,7 +2936,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2943,10 +2948,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2964,7 +2969,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -2973,13 +2978,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -2997,19 +3002,19 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>44</v>
@@ -3030,7 +3035,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3039,13 +3044,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3063,22 +3068,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3111,7 +3116,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3123,10 +3128,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3144,7 +3149,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3156,10 +3161,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3177,7 +3182,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3192,7 +3197,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3210,7 +3215,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3222,10 +3227,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3243,7 +3248,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3255,7 +3260,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>24</v>
@@ -3276,7 +3281,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3288,10 +3293,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3309,7 +3314,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3321,7 +3326,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J59" s="7">
         <v>28</v>
@@ -3342,7 +3347,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3354,10 +3359,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3390,7 +3395,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3402,14 +3407,18 @@
         <v>23</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>119</v>
-      </c>
-      <c r="K62" s="7"/>
+        <v>120</v>
+      </c>
+      <c t="s" r="K62" s="7">
+        <v>121</v>
+      </c>
       <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
+      <c t="s" r="M62" s="7">
+        <v>122</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
@@ -3423,7 +3432,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3435,10 +3444,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3456,7 +3465,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3468,7 +3477,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>48</v>
@@ -3504,7 +3513,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3516,10 +3525,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3537,7 +3546,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3549,10 +3558,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3570,7 +3579,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3582,10 +3591,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3603,7 +3612,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3615,10 +3624,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3636,7 +3645,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3645,13 +3654,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3669,22 +3678,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3702,7 +3711,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3714,10 +3723,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3735,7 +3744,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3747,10 +3756,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3783,7 +3792,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3792,13 +3801,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3816,22 +3825,22 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3849,7 +3858,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3864,11 +3873,15 @@
         <v>36</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>142</v>
-      </c>
-      <c r="K77" s="7"/>
+        <v>145</v>
+      </c>
+      <c t="s" r="K77" s="7">
+        <v>146</v>
+      </c>
       <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
+      <c t="s" r="M77" s="7">
+        <v>25</v>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
@@ -3882,7 +3895,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3894,10 +3907,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3915,7 +3928,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3927,10 +3940,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3963,7 +3976,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3972,10 +3985,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>36</v>
@@ -3996,22 +4009,22 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4029,7 +4042,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4038,13 +4051,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4062,22 +4075,22 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4095,7 +4108,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4104,13 +4117,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4128,22 +4141,22 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4176,7 +4189,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4188,10 +4201,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4209,7 +4222,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4221,10 +4234,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4242,7 +4255,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4254,7 +4267,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>22</v>
@@ -4275,7 +4288,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4284,13 +4297,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4308,22 +4321,22 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4356,7 +4369,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4368,10 +4381,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4389,7 +4402,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4398,13 +4411,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4422,22 +4435,22 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4455,7 +4468,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4467,10 +4480,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4503,7 +4516,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4518,7 +4531,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4536,7 +4549,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4548,10 +4561,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4569,7 +4582,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4578,13 +4591,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4602,22 +4615,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4635,7 +4648,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4644,13 +4657,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4668,22 +4681,22 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4701,7 +4714,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4710,13 +4723,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4734,22 +4747,22 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4782,7 +4795,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4794,7 +4807,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>36</v>
@@ -4815,7 +4828,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4824,13 +4837,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4844,26 +4857,26 @@
         <v>6868</v>
       </c>
       <c t="s" r="C110" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4877,11 +4890,11 @@
         <v>6868</v>
       </c>
       <c t="s" r="C111" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4890,13 +4903,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4910,26 +4923,26 @@
         <v>6847</v>
       </c>
       <c t="s" r="C112" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4962,7 +4975,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4974,10 +4987,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4995,7 +5008,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5007,10 +5020,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5028,7 +5041,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5037,13 +5050,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5061,22 +5074,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5094,7 +5107,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5103,13 +5116,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5127,13 +5140,13 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>23</v>
@@ -5142,7 +5155,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5160,7 +5173,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5169,13 +5182,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5193,19 +5206,19 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>59</v>
@@ -5241,7 +5254,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5253,7 +5266,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>52</v>
@@ -5274,7 +5287,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5283,13 +5296,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5307,13 +5320,13 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>17</v>
@@ -5322,7 +5335,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5340,7 +5353,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5349,13 +5362,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5388,7 +5401,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5400,10 +5413,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5421,7 +5434,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5433,10 +5446,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5454,7 +5467,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5466,10 +5479,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5487,7 +5500,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5499,7 +5512,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>54</v>
@@ -5520,7 +5533,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5532,10 +5545,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5553,7 +5566,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5565,10 +5578,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5586,7 +5599,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5595,13 +5608,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5619,19 +5632,19 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>27</v>
@@ -5667,7 +5680,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5679,10 +5692,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5700,7 +5713,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5712,10 +5725,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5733,7 +5746,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5742,13 +5755,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5766,22 +5779,22 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5799,7 +5812,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5814,7 +5827,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5832,7 +5845,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5844,7 +5857,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>45</v>
@@ -5880,7 +5893,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5892,7 +5905,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>52</v>
@@ -5913,7 +5926,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5922,13 +5935,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5946,19 +5959,19 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>53</v>
@@ -5979,22 +5992,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6012,22 +6025,22 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6045,7 +6058,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6054,13 +6067,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6078,22 +6091,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6111,7 +6124,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6123,10 +6136,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6159,7 +6172,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6168,13 +6181,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6192,19 +6205,19 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>34</v>
@@ -6225,7 +6238,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6234,13 +6247,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6258,22 +6271,22 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6291,7 +6304,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6306,7 +6319,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6324,7 +6337,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6336,10 +6349,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6368,26 +6381,26 @@
         <v>6889</v>
       </c>
       <c t="s" r="C160" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6401,11 +6414,11 @@
         <v>6889</v>
       </c>
       <c t="s" r="C161" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6414,13 +6427,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6438,19 +6451,19 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>43</v>
@@ -6471,7 +6484,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6480,13 +6493,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6519,22 +6532,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6552,7 +6565,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6561,13 +6574,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6585,22 +6598,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6633,7 +6646,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6642,13 +6655,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6666,22 +6679,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6699,7 +6712,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6708,13 +6721,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6732,13 +6745,13 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>20</v>
@@ -6747,7 +6760,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6765,7 +6778,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6777,10 +6790,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6813,7 +6826,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6822,13 +6835,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6846,22 +6859,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6879,7 +6892,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6888,13 +6901,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6912,22 +6925,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6945,7 +6958,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6954,13 +6967,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6978,22 +6991,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7011,7 +7024,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7020,13 +7033,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7044,22 +7057,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7092,7 +7105,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7104,10 +7117,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7125,7 +7138,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7137,10 +7150,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7158,7 +7171,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7173,7 +7186,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7206,7 +7219,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7215,13 +7228,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7239,22 +7252,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7272,7 +7285,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7287,7 +7300,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7305,7 +7318,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7317,10 +7330,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7338,7 +7351,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7347,13 +7360,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7371,19 +7384,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>27</v>
@@ -7419,7 +7432,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7428,13 +7441,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7452,22 +7465,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7485,7 +7498,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7494,13 +7507,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7518,13 +7531,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>35</v>
@@ -7533,7 +7546,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7551,7 +7564,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7566,7 +7579,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7599,7 +7612,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7611,10 +7624,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7632,7 +7645,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7644,7 +7657,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>34</v>
@@ -7665,7 +7678,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7674,13 +7687,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7698,22 +7711,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7746,7 +7759,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7758,7 +7771,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>18</v>
@@ -7779,7 +7792,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7791,10 +7804,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7812,7 +7825,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7824,10 +7837,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7845,7 +7858,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7857,10 +7870,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7878,7 +7891,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7887,13 +7900,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7911,22 +7924,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7944,7 +7957,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7956,7 +7969,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>44</v>
@@ -7992,22 +8005,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8025,22 +8038,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8058,19 +8071,19 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>31</v>
@@ -8106,7 +8119,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8115,13 +8128,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8139,22 +8152,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8172,7 +8185,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8184,10 +8197,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8205,7 +8218,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8217,10 +8230,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8238,7 +8251,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8247,13 +8260,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8271,22 +8284,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8319,7 +8332,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8331,10 +8344,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8352,7 +8365,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8361,13 +8374,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8385,22 +8398,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8418,7 +8431,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8427,10 +8440,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>57</v>
@@ -8451,22 +8464,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8499,7 +8512,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8511,10 +8524,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8532,7 +8545,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8541,10 +8554,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>22</v>
@@ -8565,19 +8578,19 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>44</v>
@@ -8598,7 +8611,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8610,10 +8623,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8646,7 +8659,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8655,13 +8668,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8679,22 +8692,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8712,7 +8725,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8721,10 +8734,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>48</v>
@@ -8745,22 +8758,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8793,7 +8806,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8808,7 +8821,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8826,7 +8839,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8835,13 +8848,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8859,22 +8872,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8892,7 +8905,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8901,13 +8914,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8925,22 +8938,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8973,7 +8986,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -8982,13 +8995,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9006,19 +9019,19 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>34</v>
@@ -9039,7 +9052,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9048,13 +9061,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9072,22 +9085,22 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9105,7 +9118,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9117,10 +9130,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9138,7 +9151,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9150,10 +9163,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9171,7 +9184,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9180,13 +9193,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9215,11 +9228,11 @@
         <v>6756</v>
       </c>
       <c t="s" r="C255" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9228,13 +9241,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9248,17 +9261,17 @@
         <v>6757</v>
       </c>
       <c t="s" r="C256" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>20</v>
@@ -9267,7 +9280,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9300,7 +9313,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9309,13 +9322,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9333,22 +9346,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9366,7 +9379,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9375,13 +9388,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9399,22 +9412,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9447,7 +9460,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9456,13 +9469,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9480,22 +9493,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9513,7 +9526,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9522,13 +9535,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9546,22 +9559,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9579,7 +9592,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9591,10 +9604,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9612,7 +9625,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9624,10 +9637,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9660,7 +9673,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9672,10 +9685,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9693,7 +9706,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9705,10 +9718,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9726,7 +9739,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9738,10 +9751,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9759,7 +9772,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9771,10 +9784,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9792,7 +9805,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9804,10 +9817,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9825,7 +9838,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9837,10 +9850,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9858,7 +9871,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9870,10 +9883,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9906,7 +9919,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -9915,13 +9928,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9939,19 +9952,19 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>53</v>
@@ -9972,7 +9985,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -9984,10 +9997,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10005,7 +10018,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10020,7 +10033,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10038,7 +10051,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10050,10 +10063,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10071,7 +10084,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10083,10 +10096,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10119,7 +10132,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10128,13 +10141,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10152,19 +10165,19 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>37</v>
@@ -10185,7 +10198,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10197,10 +10210,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10218,7 +10231,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10233,7 +10246,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10251,7 +10264,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10263,10 +10276,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10284,7 +10297,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10296,10 +10309,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10317,7 +10330,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10326,13 +10339,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10365,7 +10378,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10374,13 +10387,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10398,22 +10411,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10431,7 +10444,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10440,13 +10453,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10464,22 +10477,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10497,7 +10510,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10506,13 +10519,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10530,22 +10543,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10578,7 +10591,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10611,7 +10624,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10620,10 +10633,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>40</v>
@@ -10644,22 +10657,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10677,7 +10690,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10689,10 +10702,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10725,7 +10738,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10734,13 +10747,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10758,19 +10771,19 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>18</v>
@@ -10791,7 +10804,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10803,10 +10816,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10839,7 +10852,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10848,13 +10861,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10872,22 +10885,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10905,7 +10918,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10914,13 +10927,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10938,22 +10951,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10971,7 +10984,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -10980,10 +10993,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>28</v>
@@ -11004,22 +11017,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11052,7 +11065,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11064,10 +11077,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11085,7 +11098,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11094,13 +11107,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11118,13 +11131,13 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>23</v>
@@ -11133,7 +11146,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11151,7 +11164,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11163,10 +11176,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11184,7 +11197,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11196,10 +11209,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11217,7 +11230,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11229,10 +11242,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11265,7 +11278,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11274,13 +11287,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11298,13 +11311,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>20</v>
@@ -11313,7 +11326,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11331,7 +11344,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11343,10 +11356,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11364,7 +11377,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11376,10 +11389,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11397,7 +11410,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11412,7 +11425,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11430,7 +11443,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11442,10 +11455,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11474,17 +11487,17 @@
         <v>28</v>
       </c>
       <c t="s" r="C330" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
@@ -11493,7 +11506,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11511,7 +11524,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11523,10 +11536,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11559,7 +11572,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11568,13 +11581,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11592,22 +11605,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11625,7 +11638,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11634,10 +11647,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>41</v>
@@ -11658,22 +11671,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11706,7 +11719,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11715,13 +11728,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11739,22 +11752,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11772,22 +11785,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11805,13 +11818,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
@@ -11820,7 +11833,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11838,7 +11851,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11847,7 +11860,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>55</v>
@@ -11871,22 +11884,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11904,7 +11917,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11916,10 +11929,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11937,7 +11950,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -11949,10 +11962,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11985,7 +11998,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -11994,10 +12007,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>54</v>
@@ -12018,22 +12031,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12051,7 +12064,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12066,7 +12079,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12084,7 +12097,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12096,10 +12109,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12132,7 +12145,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12141,13 +12154,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12165,19 +12178,19 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>54</v>
@@ -12198,7 +12211,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12207,10 +12220,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>55</v>
@@ -12231,22 +12244,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12264,7 +12277,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12276,10 +12289,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12297,7 +12310,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12309,10 +12322,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12345,7 +12358,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12357,10 +12370,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12378,7 +12391,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12387,13 +12400,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12411,19 +12424,19 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>24</v>
@@ -12444,7 +12457,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12453,13 +12466,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12477,19 +12490,19 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>58</v>
@@ -12510,7 +12523,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12519,13 +12532,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12558,7 +12571,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12567,13 +12580,13 @@
         <v>62</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12591,22 +12604,22 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12624,7 +12637,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12633,10 +12646,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>55</v>
@@ -12657,13 +12670,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>23</v>
@@ -12672,7 +12685,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12690,7 +12703,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12699,13 +12712,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12723,22 +12736,22 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12771,7 +12784,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12783,10 +12796,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12804,7 +12817,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12813,13 +12826,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12837,22 +12850,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12870,7 +12883,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12879,13 +12892,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12903,22 +12916,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12951,7 +12964,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12963,10 +12976,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12984,7 +12997,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -12996,10 +13009,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13017,7 +13030,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13029,10 +13042,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13050,7 +13063,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13062,10 +13075,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13098,7 +13111,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13107,13 +13120,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13131,13 +13144,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>23</v>
@@ -13146,7 +13159,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13164,7 +13177,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13176,10 +13189,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13197,7 +13210,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13206,13 +13219,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13230,22 +13243,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13278,7 +13291,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13287,13 +13300,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13311,22 +13324,22 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13344,7 +13357,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13353,13 +13366,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13377,19 +13390,19 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>60</v>
@@ -13425,7 +13438,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13440,7 +13453,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13458,7 +13471,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -13470,10 +13483,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13487,11 +13500,11 @@
         <v>6851</v>
       </c>
       <c t="s" r="C397" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -13500,13 +13513,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13520,26 +13533,26 @@
         <v>6852</v>
       </c>
       <c t="s" r="C398" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13572,22 +13585,22 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13605,22 +13618,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13653,13 +13666,13 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>23</v>
@@ -13668,7 +13681,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13686,7 +13699,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13695,13 +13708,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13734,7 +13747,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -13743,13 +13756,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13767,22 +13780,22 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13800,22 +13813,22 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13848,19 +13861,19 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>21</v>
@@ -13881,7 +13894,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -13890,13 +13903,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13929,7 +13942,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -13941,10 +13954,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -13962,7 +13975,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -13974,10 +13987,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13995,7 +14008,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14007,10 +14020,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14028,7 +14041,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14040,10 +14053,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14061,7 +14074,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14094,7 +14107,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14106,10 +14119,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14142,7 +14155,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14154,10 +14167,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14175,7 +14188,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14187,10 +14200,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14208,7 +14221,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14217,13 +14230,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14241,22 +14254,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14289,7 +14302,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -14298,13 +14311,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14322,13 +14335,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>23</v>
@@ -14337,7 +14350,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14345,7 +14358,7 @@
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c t="s" r="A427" s="9">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
@@ -14365,7 +14378,7 @@
     <row r="428" ht="65.25" customHeight="1"/>
     <row r="429" ht="16.5" customHeight="1">
       <c t="s" r="A429" s="10">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B429" s="10"/>
       <c r="C429" s="10"/>
@@ -14378,7 +14391,7 @@
       <c r="J429" s="10"/>
       <c r="K429" s="10"/>
       <c t="s" r="L429" s="11">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M429" s="11"/>
       <c r="N429" s="11"/>

--- a/Data/FlightPlan/FPL_28OCT26.xlsx
+++ b/Data/FlightPlan/FPL_28OCT26.xlsx
@@ -272,7 +272,7 @@
     <t>11:35</t>
   </si>
   <si>
-    <t>12:35</t>
+    <t>12:29</t>
   </si>
   <si>
     <t>CNX</t>
@@ -440,6 +440,9 @@
     <t>10:10</t>
   </si>
   <si>
+    <t>12:07</t>
+  </si>
+  <si>
     <t>12:50</t>
   </si>
   <si>
@@ -542,6 +545,9 @@
     <t>11:50</t>
   </si>
   <si>
+    <t>11:52</t>
+  </si>
+  <si>
     <t>14:15</t>
   </si>
   <si>
@@ -596,6 +602,9 @@
     <t>10:49</t>
   </si>
   <si>
+    <t>12:31</t>
+  </si>
+  <si>
     <t>12:55</t>
   </si>
   <si>
@@ -623,6 +632,9 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>12:08</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
@@ -647,7 +659,7 @@
     <t>09:44</t>
   </si>
   <si>
-    <t>11:51</t>
+    <t>12:36</t>
   </si>
   <si>
     <t>PXU</t>
@@ -704,9 +716,18 @@
     <t>07:01</t>
   </si>
   <si>
+    <t>11:07</t>
+  </si>
+  <si>
     <t>14:50</t>
   </si>
   <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
     <t>17:10</t>
   </si>
   <si>
@@ -752,6 +773,9 @@
     <t>10:05</t>
   </si>
   <si>
+    <t>12:19</t>
+  </si>
+  <si>
     <t>11:55</t>
   </si>
   <si>
@@ -785,297 +809,312 @@
     <t>09:45</t>
   </si>
   <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>09:47</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>DVO</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>07:23</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>13:31</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
     <t>11:25</t>
   </si>
   <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>14:21</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>09:47</t>
-  </si>
-  <si>
-    <t>DVO</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>07:23</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>12:28</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>11:08</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:37</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>13:31</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
     <t>23:00</t>
   </si>
   <si>
@@ -1139,6 +1178,9 @@
     <t>09:19</t>
   </si>
   <si>
+    <t>11:53</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1187,6 +1229,9 @@
     <t>10:25</t>
   </si>
   <si>
+    <t>12:26</t>
+  </si>
+  <si>
     <t>23:25</t>
   </si>
   <si>
@@ -1196,6 +1241,9 @@
     <t>CGK</t>
   </si>
   <si>
+    <t>12:49</t>
+  </si>
+  <si>
     <t>22:10</t>
   </si>
   <si>
@@ -1205,6 +1253,9 @@
     <t>10:53</t>
   </si>
   <si>
+    <t>19:45</t>
+  </si>
+  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1238,9 +1289,6 @@
     <t>VN-A687</t>
   </si>
   <si>
-    <t>19:45</t>
-  </si>
-  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1253,12 +1301,18 @@
     <t>VN-A697</t>
   </si>
   <si>
+    <t>14:41</t>
+  </si>
+  <si>
     <t>DEL</t>
   </si>
   <si>
     <t>VN-A810</t>
   </si>
   <si>
+    <t>10:46</t>
+  </si>
+  <si>
     <t>KJA</t>
   </si>
   <si>
@@ -1289,6 +1343,9 @@
     <t>OVB</t>
   </si>
   <si>
+    <t>18:12</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1316,13 +1373,16 @@
     <t>BNE</t>
   </si>
   <si>
+    <t>22:22</t>
+  </si>
+  <si>
     <t>05:05</t>
   </si>
   <si>
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 28, 2026 09:53</t>
+    <t xml:space="preserve">Generated on  Oct 28, 2026 11:21</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3345,7 +3405,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3780,7 +3840,9 @@
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
+      <c t="s" r="M68" s="7">
+        <v>143</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c t="s" r="A69" s="6">
@@ -3806,10 +3868,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3876,17 +3938,17 @@
         <v>24</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="K71" s="7">
         <v>23</v>
       </c>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -3916,7 +3978,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3949,7 +4011,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3958,18 +4020,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="I74" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -3984,27 +4046,27 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4019,7 +4081,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4034,10 +4096,10 @@
         <v>38</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="K76" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
@@ -4056,7 +4118,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4068,10 +4130,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4089,7 +4151,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4101,10 +4163,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4137,7 +4199,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4146,10 +4208,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>38</v>
@@ -4157,7 +4219,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4172,22 +4234,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4205,7 +4267,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4214,13 +4276,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="I82" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4238,19 +4300,19 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>111</v>
@@ -4271,7 +4333,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4280,13 +4342,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4304,22 +4366,22 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4352,7 +4414,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4364,10 +4426,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4385,7 +4447,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4400,11 +4462,13 @@
         <v>83</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
+      <c t="s" r="M88" s="7">
+        <v>178</v>
+      </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c t="s" r="A89" s="6">
@@ -4418,7 +4482,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4430,10 +4494,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4451,7 +4515,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4466,14 +4530,14 @@
         <v>86</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="K90" s="7">
         <v>130</v>
       </c>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4488,7 +4552,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4500,7 +4564,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>23</v>
@@ -4510,7 +4574,7 @@
       </c>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4525,7 +4589,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4534,20 +4598,20 @@
         <v>24</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4562,25 +4626,25 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="K93" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
@@ -4614,7 +4678,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4626,10 +4690,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4649,7 +4713,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4658,13 +4722,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4682,22 +4746,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4715,7 +4779,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4727,10 +4791,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4763,7 +4827,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4778,12 +4842,12 @@
         <v>54</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4798,7 +4862,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4810,7 +4874,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>83</v>
@@ -4818,7 +4882,7 @@
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4833,7 +4897,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4842,7 +4906,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>131</v>
@@ -4852,7 +4916,9 @@
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
+      <c t="s" r="M102" s="7">
+        <v>197</v>
+      </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c t="s" r="A103" s="6">
@@ -4866,19 +4932,19 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>97</v>
@@ -4899,7 +4965,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4908,13 +4974,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4932,22 +4998,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4965,7 +5031,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4977,10 +5043,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4998,7 +5064,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5010,7 +5076,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>94</v>
@@ -5046,7 +5112,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5058,14 +5124,16 @@
         <v>24</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>38</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
+      <c t="s" r="M109" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c t="s" r="A110" s="6">
@@ -5079,7 +5147,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5108,11 +5176,11 @@
         <v>6868</v>
       </c>
       <c t="s" r="C111" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5124,7 +5192,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>102</v>
@@ -5141,11 +5209,11 @@
         <v>6868</v>
       </c>
       <c t="s" r="C112" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5154,13 +5222,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5174,26 +5242,26 @@
         <v>6847</v>
       </c>
       <c t="s" r="C113" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5226,7 +5294,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5241,12 +5309,12 @@
         <v>118</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5261,7 +5329,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5273,15 +5341,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5296,7 +5364,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5305,13 +5373,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5329,22 +5397,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5362,7 +5430,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5371,13 +5439,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5395,13 +5463,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>24</v>
@@ -5410,7 +5478,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5428,7 +5496,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5437,13 +5505,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5461,19 +5529,19 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>62</v>
@@ -5509,7 +5577,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5521,7 +5589,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>54</v>
@@ -5529,7 +5597,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5544,7 +5612,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5556,15 +5624,15 @@
         <v>93</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5579,7 +5647,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5594,7 +5662,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5612,7 +5680,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5624,10 +5692,10 @@
         <v>93</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5660,7 +5728,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5672,15 +5740,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5695,7 +5763,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5710,7 +5778,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5730,7 +5798,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5742,14 +5810,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>69</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
-      <c r="M131" s="7"/>
+      <c t="s" r="M131" s="7">
+        <v>235</v>
+      </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c t="s" r="A132" s="6">
@@ -5763,7 +5833,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5780,9 +5850,13 @@
       <c t="s" r="J132" s="7">
         <v>57</v>
       </c>
-      <c r="K132" s="7"/>
+      <c t="s" r="K132" s="7">
+        <v>55</v>
+      </c>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -5796,7 +5870,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5808,14 +5882,18 @@
         <v>27</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>231</v>
-      </c>
-      <c r="K133" s="7"/>
+        <v>236</v>
+      </c>
+      <c t="s" r="K133" s="7">
+        <v>237</v>
+      </c>
       <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
+      <c t="s" r="M133" s="7">
+        <v>238</v>
+      </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c t="s" r="A134" s="6">
@@ -5829,7 +5907,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5841,14 +5919,18 @@
         <v>21</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>232</v>
-      </c>
-      <c r="K134" s="7"/>
+        <v>239</v>
+      </c>
+      <c t="s" r="K134" s="7">
+        <v>218</v>
+      </c>
       <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
+      <c t="s" r="M134" s="7">
+        <v>147</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
@@ -5862,7 +5944,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5871,13 +5953,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5895,13 +5977,13 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>21</v>
@@ -5943,7 +6025,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5955,15 +6037,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -5978,7 +6060,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5990,15 +6072,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6013,7 +6095,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6022,10 +6104,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>90</v>
@@ -6046,13 +6128,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
@@ -6061,7 +6143,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6079,7 +6161,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6094,7 +6176,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6112,7 +6194,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6124,7 +6206,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>47</v>
@@ -6160,7 +6242,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6172,7 +6254,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>54</v>
@@ -6180,7 +6262,7 @@
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6195,7 +6277,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6204,18 +6286,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I146" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6230,29 +6312,29 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>124</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>55</v>
       </c>
       <c t="s" r="K147" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>71</v>
+        <v>254</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6267,7 +6349,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6276,16 +6358,16 @@
         <v>124</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
@@ -6304,22 +6386,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6337,7 +6419,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6349,7 +6431,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>103</v>
@@ -6370,7 +6452,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6382,10 +6464,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6403,7 +6485,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6418,7 +6500,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6451,7 +6533,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6460,10 +6542,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>140</v>
@@ -6471,7 +6553,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6486,13 +6568,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>17</v>
@@ -6504,11 +6586,11 @@
         <v>35</v>
       </c>
       <c t="s" r="K155" s="7">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6523,7 +6605,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6535,17 +6617,17 @@
         <v>124</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>89</v>
       </c>
       <c t="s" r="K156" s="7">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6560,7 +6642,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6597,7 +6679,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6612,14 +6694,14 @@
         <v>23</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="K158" s="7">
         <v>41</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6634,7 +6716,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6649,14 +6731,14 @@
         <v>126</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="K159" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6682,31 +6764,31 @@
         <v>6889</v>
       </c>
       <c t="s" r="C161" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6717,11 +6799,11 @@
         <v>6889</v>
       </c>
       <c t="s" r="C162" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6754,7 +6836,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6766,7 +6848,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>45</v>
@@ -6787,7 +6869,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6796,13 +6878,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6835,7 +6917,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6847,15 +6929,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6870,7 +6952,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6879,13 +6961,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6903,19 +6985,19 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>46</v>
@@ -6951,7 +7033,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6960,18 +7042,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -6986,13 +7068,13 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>21</v>
@@ -7001,11 +7083,13 @@
         <v>131</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
-      <c r="M171" s="7"/>
+      <c t="s" r="M171" s="7">
+        <v>287</v>
+      </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c t="s" r="A172" s="6">
@@ -7015,11 +7099,11 @@
         <v>6756</v>
       </c>
       <c t="s" r="C172" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7028,13 +7112,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c t="s" r="K172" s="7">
         <v>97</v>
@@ -7052,17 +7136,17 @@
         <v>6757</v>
       </c>
       <c t="s" r="C173" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>21</v>
@@ -7071,14 +7155,14 @@
         <v>60</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c t="s" r="K173" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7108,7 +7192,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7120,15 +7204,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7143,7 +7227,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7163,7 +7247,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7178,7 +7262,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7193,14 +7277,14 @@
         <v>35</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="K177" s="7">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7215,7 +7299,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7230,10 +7314,10 @@
         <v>89</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
@@ -7252,7 +7336,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7267,14 +7351,14 @@
         <v>123</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c t="s" r="K179" s="7">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7289,7 +7373,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7304,14 +7388,14 @@
         <v>110</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c t="s" r="K180" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7326,7 +7410,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7341,7 +7425,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7359,7 +7443,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7371,10 +7455,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7407,7 +7491,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7422,11 +7506,13 @@
         <v>69</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
+      <c t="s" r="M184" s="7">
+        <v>303</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
@@ -7440,7 +7526,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7452,7 +7538,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>90</v>
@@ -7473,7 +7559,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7488,7 +7574,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7506,7 +7592,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7518,7 +7604,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>136</v>
@@ -7554,7 +7640,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7569,12 +7655,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7589,7 +7675,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7609,7 +7695,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7624,7 +7710,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7639,7 +7725,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7657,7 +7743,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7669,7 +7755,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>123</v>
@@ -7690,7 +7776,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7699,13 +7785,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7723,13 +7809,13 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>17</v>
@@ -7771,7 +7857,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7783,10 +7869,10 @@
         <v>124</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7804,7 +7890,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7816,7 +7902,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>90</v>
@@ -7837,7 +7923,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7846,13 +7932,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>123</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7870,13 +7956,13 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>37</v>
@@ -7885,7 +7971,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7903,7 +7989,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7918,7 +8004,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7951,7 +8037,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7963,15 +8049,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7986,7 +8072,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7998,7 +8084,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>35</v>
@@ -8006,7 +8092,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8021,7 +8107,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8030,13 +8116,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8054,13 +8140,13 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>21</v>
@@ -8069,7 +8155,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8102,7 +8188,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8114,7 +8200,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>18</v>
@@ -8122,7 +8208,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8137,7 +8223,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8149,14 +8235,16 @@
         <v>27</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
-      <c r="M208" s="7"/>
+      <c t="s" r="M208" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c t="s" r="A209" s="6">
@@ -8170,7 +8258,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8203,7 +8291,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8212,20 +8300,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="K210" s="7">
         <v>58</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8240,13 +8328,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>21</v>
@@ -8255,14 +8343,14 @@
         <v>42</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="K211" s="7">
         <v>102</v>
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8292,7 +8380,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8301,10 +8389,10 @@
         <v>99</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>73</v>
@@ -8325,13 +8413,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>99</v>
@@ -8340,7 +8428,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8358,7 +8446,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8370,7 +8458,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>32</v>
@@ -8406,7 +8494,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8426,7 +8514,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8441,7 +8529,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8453,7 +8541,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>140</v>
@@ -8476,7 +8564,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8488,14 +8576,16 @@
         <v>53</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
-      <c r="M219" s="7"/>
+      <c t="s" r="M219" s="7">
+        <v>165</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c t="s" r="A220" s="6">
@@ -8509,7 +8599,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8521,10 +8611,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8542,7 +8632,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8551,13 +8641,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c t="s" r="I221" s="7">
         <v>123</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8575,13 +8665,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>24</v>
@@ -8590,7 +8680,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8623,7 +8713,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8635,15 +8725,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8658,7 +8748,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8667,17 +8757,19 @@
         <v>21</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>85</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>336</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
@@ -8691,22 +8783,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8724,7 +8816,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8733,10 +8825,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>60</v>
@@ -8757,22 +8849,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8790,7 +8882,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8802,10 +8894,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8838,7 +8930,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8850,10 +8942,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8873,7 +8965,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8882,17 +8974,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>23</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
-      <c r="M232" s="7"/>
+      <c t="s" r="M232" s="7">
+        <v>341</v>
+      </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
@@ -8906,19 +9000,19 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>46</v>
@@ -8939,7 +9033,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8951,10 +9045,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8987,7 +9081,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8996,18 +9090,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9022,13 +9116,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>24</v>
@@ -9055,7 +9149,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9064,10 +9158,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>50</v>
@@ -9088,19 +9182,19 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>118</v>
@@ -9136,7 +9230,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9151,12 +9245,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9171,7 +9265,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9180,7 +9274,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>38</v>
@@ -9204,19 +9298,19 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>102</v>
@@ -9237,7 +9331,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9246,13 +9340,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9270,22 +9364,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9318,7 +9412,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9330,15 +9424,15 @@
         <v>108</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9353,7 +9447,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9365,7 +9459,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>35</v>
@@ -9373,7 +9467,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9388,7 +9482,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9400,10 +9494,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9421,7 +9515,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9436,7 +9530,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9454,7 +9548,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9466,10 +9560,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9487,7 +9581,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9499,10 +9593,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9520,7 +9614,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9532,10 +9626,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9568,7 +9662,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9580,7 +9674,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>25</v>
@@ -9601,7 +9695,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9613,7 +9707,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>127</v>
@@ -9634,7 +9728,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9646,7 +9740,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>29</v>
@@ -9667,7 +9761,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9679,7 +9773,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>94</v>
@@ -9715,7 +9809,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9724,18 +9818,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9750,13 +9844,13 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>24</v>
@@ -9765,7 +9859,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9783,7 +9877,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9792,13 +9886,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>75</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9816,19 +9910,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>136</v>
@@ -9864,7 +9958,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9873,13 +9967,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9897,22 +9991,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9930,7 +10024,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9939,13 +10033,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9963,19 +10057,19 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>103</v>
@@ -9996,7 +10090,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10008,10 +10102,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10029,7 +10123,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10044,7 +10138,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10077,7 +10171,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10089,10 +10183,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10112,7 +10206,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10124,14 +10218,16 @@
         <v>44</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>258</v>
+        <v>367</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
-      <c r="M273" s="7"/>
+      <c t="s" r="M273" s="7">
+        <v>86</v>
+      </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c t="s" r="A274" s="6">
@@ -10145,7 +10241,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10157,10 +10253,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10178,7 +10274,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10187,7 +10283,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>130</v>
@@ -10211,13 +10307,13 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>24</v>
@@ -10226,7 +10322,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10244,7 +10340,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10256,10 +10352,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10277,7 +10373,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10289,10 +10385,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10325,7 +10421,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10334,18 +10430,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10360,19 +10456,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>55</v>
@@ -10380,7 +10476,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>358</v>
+        <v>371</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10395,7 +10491,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10410,7 +10506,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10428,7 +10524,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10443,7 +10539,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10461,7 +10557,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10473,7 +10569,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>127</v>
@@ -10494,7 +10590,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10506,7 +10602,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>80</v>
@@ -10527,7 +10623,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10542,7 +10638,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10575,7 +10671,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10584,7 +10680,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>34</v>
@@ -10595,7 +10691,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>360</v>
+        <v>373</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10610,13 +10706,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>17</v>
@@ -10630,7 +10726,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10645,7 +10741,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10657,10 +10753,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10678,7 +10774,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10693,7 +10789,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10711,7 +10807,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10726,7 +10822,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10744,7 +10840,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10756,10 +10852,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10777,7 +10873,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10789,7 +10885,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>96</v>
@@ -10825,7 +10921,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10834,13 +10930,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>137</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10860,22 +10956,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10895,7 +10991,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10904,10 +11000,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>123</v>
@@ -10928,13 +11024,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>17</v>
@@ -10961,7 +11057,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10970,13 +11066,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10994,13 +11090,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>17</v>
@@ -11009,7 +11105,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11042,7 +11138,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11062,7 +11158,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>367</v>
+        <v>380</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11077,7 +11173,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11086,10 +11182,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>42</v>
@@ -11110,22 +11206,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11143,7 +11239,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11155,10 +11251,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11191,7 +11287,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11200,10 +11296,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>139</v>
@@ -11211,7 +11307,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11226,19 +11322,19 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>18</v>
@@ -11246,7 +11342,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11261,7 +11357,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11273,14 +11369,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>120</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
-      <c r="M310" s="7"/>
+      <c t="s" r="M310" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
       <c r="A311" s="6"/>
@@ -11309,7 +11407,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11318,10 +11416,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>118</v>
@@ -11329,7 +11427,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11344,27 +11442,27 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11379,7 +11477,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11388,17 +11486,19 @@
         <v>24</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>86</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
-      <c r="M314" s="7"/>
+      <c t="s" r="M314" s="7">
+        <v>389</v>
+      </c>
     </row>
     <row r="315" ht="15" customHeight="1">
       <c t="s" r="A315" s="6">
@@ -11412,13 +11512,13 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>24</v>
@@ -11445,7 +11545,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11454,7 +11554,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c t="s" r="I316" s="7">
         <v>109</v>
@@ -11478,22 +11578,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11526,7 +11626,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11546,7 +11646,7 @@
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11561,7 +11661,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11570,13 +11670,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>131</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11594,13 +11694,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>24</v>
@@ -11627,7 +11727,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11642,7 +11742,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11660,7 +11760,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11675,7 +11775,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11693,7 +11793,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11705,10 +11805,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11741,7 +11841,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11753,14 +11853,16 @@
         <v>99</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
-      <c r="M326" s="7"/>
+      <c t="s" r="M326" s="7">
+        <v>164</v>
+      </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
       <c t="s" r="A327" s="6">
@@ -11774,7 +11876,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11789,7 +11891,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11807,7 +11909,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11819,10 +11921,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11840,7 +11942,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11852,10 +11954,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11873,7 +11975,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11888,7 +11990,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11906,7 +12008,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11918,7 +12020,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>113</v>
@@ -11950,17 +12052,17 @@
         <v>28</v>
       </c>
       <c t="s" r="C333" s="7">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>17</v>
@@ -11987,7 +12089,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11999,10 +12101,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12035,7 +12137,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12047,15 +12149,15 @@
         <v>70</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>387</v>
+        <v>401</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12070,7 +12172,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12082,10 +12184,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12103,7 +12205,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12112,7 +12214,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>97</v>
@@ -12136,22 +12238,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12184,7 +12286,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12193,18 +12295,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>390</v>
+        <v>404</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12219,27 +12321,27 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12254,29 +12356,29 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c t="s" r="K343" s="7">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>87</v>
+        <v>406</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12291,13 +12393,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
@@ -12309,7 +12411,7 @@
         <v>130</v>
       </c>
       <c t="s" r="K344" s="7">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
@@ -12328,7 +12430,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12337,7 +12439,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>58</v>
@@ -12350,7 +12452,7 @@
       </c>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12365,19 +12467,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>126</v>
@@ -12402,7 +12504,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12414,10 +12516,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12435,7 +12537,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12447,10 +12549,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12483,7 +12585,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12492,17 +12594,19 @@
         <v>24</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>57</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
-      <c r="M350" s="7"/>
+      <c t="s" r="M350" s="7">
+        <v>410</v>
+      </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
       <c t="s" r="A351" s="6">
@@ -12516,13 +12620,13 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>24</v>
@@ -12549,7 +12653,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12564,7 +12668,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12582,7 +12686,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12594,10 +12698,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12630,7 +12734,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12650,7 +12754,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12665,7 +12769,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12677,7 +12781,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>258</v>
+        <v>367</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>57</v>
@@ -12698,7 +12802,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12731,7 +12835,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12757,14 +12861,14 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12776,96 +12880,98 @@
         <v>21</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
-      <c t="s" r="A360" s="6">
-        <v>13</v>
-      </c>
-      <c r="B360" s="7">
-        <v>623</v>
-      </c>
-      <c t="s" r="C360" s="7">
-        <v>14</v>
-      </c>
+      <c r="A360" s="6"/>
+      <c r="B360" s="7"/>
+      <c r="C360" s="7"/>
       <c r="D360" s="7"/>
-      <c t="s" r="E360" s="7">
-        <v>396</v>
-      </c>
-      <c r="F360" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G360" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H360" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I360" s="7">
-        <v>240</v>
-      </c>
-      <c t="s" r="J360" s="7">
-        <v>182</v>
-      </c>
+      <c r="E360" s="7"/>
+      <c r="F360" s="7"/>
+      <c r="G360" s="8"/>
+      <c r="H360" s="8"/>
+      <c r="I360" s="7"/>
+      <c r="J360" s="7"/>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c r="M360" s="7"/>
     </row>
     <row r="361" ht="14.25" customHeight="1">
-      <c r="A361" s="6"/>
-      <c r="B361" s="7"/>
-      <c r="C361" s="7"/>
+      <c t="s" r="A361" s="6">
+        <v>13</v>
+      </c>
+      <c r="B361" s="7">
+        <v>122</v>
+      </c>
+      <c t="s" r="C361" s="7">
+        <v>14</v>
+      </c>
       <c r="D361" s="7"/>
-      <c r="E361" s="7"/>
-      <c r="F361" s="7"/>
-      <c r="G361" s="8"/>
-      <c r="H361" s="8"/>
-      <c r="I361" s="7"/>
-      <c r="J361" s="7"/>
+      <c t="s" r="E361" s="7">
+        <v>415</v>
+      </c>
+      <c r="F361" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G361" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H361" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I361" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="J361" s="7">
+        <v>213</v>
+      </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>416</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c t="s" r="A362" s="6">
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>122</v>
+        <v>929</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>17</v>
+        <v>409</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>136</v>
+        <v>279</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>209</v>
+        <v>308</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>399</v>
+        <v>417</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12873,34 +12979,36 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
+        <v>409</v>
+      </c>
+      <c t="s" r="H363" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H363" s="8">
-        <v>394</v>
-      </c>
       <c t="s" r="I363" s="7">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>299</v>
-      </c>
-      <c r="K363" s="7"/>
+        <v>25</v>
+      </c>
+      <c t="s" r="K363" s="7">
+        <v>130</v>
+      </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>400</v>
+        <v>110</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12908,181 +13016,191 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>928</v>
+        <v>1409</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>394</v>
+        <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>25</v>
-      </c>
-      <c r="K364" s="7"/>
+        <v>248</v>
+      </c>
+      <c t="s" r="K364" s="7">
+        <v>156</v>
+      </c>
       <c r="L364" s="7"/>
-      <c r="M364" s="7"/>
+      <c t="s" r="M364" s="7">
+        <v>290</v>
+      </c>
     </row>
     <row r="365" ht="15" customHeight="1">
       <c t="s" r="A365" s="6">
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
+        <v>219</v>
+      </c>
+      <c t="s" r="H365" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H365" s="8">
-        <v>215</v>
-      </c>
       <c t="s" r="I365" s="7">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>241</v>
-      </c>
-      <c r="K365" s="7"/>
+        <v>61</v>
+      </c>
+      <c t="s" r="K365" s="7">
+        <v>29</v>
+      </c>
       <c r="L365" s="7"/>
-      <c r="M365" s="7"/>
+      <c t="s" r="M365" s="7">
+        <v>94</v>
+      </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
       <c t="s" r="A366" s="6">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B366" s="7">
-        <v>1410</v>
+        <v>958</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>215</v>
+        <v>17</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>17</v>
+        <v>418</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>61</v>
+        <v>315</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
-      <c t="s" r="A367" s="6">
-        <v>48</v>
-      </c>
-      <c r="B367" s="7">
-        <v>958</v>
-      </c>
-      <c t="s" r="C367" s="7">
-        <v>14</v>
-      </c>
+      <c r="A367" s="6"/>
+      <c r="B367" s="7"/>
+      <c r="C367" s="7"/>
       <c r="D367" s="7"/>
-      <c t="s" r="E367" s="7">
-        <v>398</v>
-      </c>
-      <c r="F367" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G367" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H367" s="8">
-        <v>401</v>
-      </c>
-      <c t="s" r="I367" s="7">
-        <v>253</v>
-      </c>
-      <c t="s" r="J367" s="7">
-        <v>306</v>
-      </c>
+      <c r="E367" s="7"/>
+      <c r="F367" s="7"/>
+      <c r="G367" s="8"/>
+      <c r="H367" s="8"/>
+      <c r="I367" s="7"/>
+      <c r="J367" s="7"/>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c r="A368" s="6"/>
-      <c r="B368" s="7"/>
-      <c r="C368" s="7"/>
+      <c t="s" r="A368" s="6">
+        <v>13</v>
+      </c>
+      <c r="B368" s="7">
+        <v>835</v>
+      </c>
+      <c t="s" r="C368" s="7">
+        <v>14</v>
+      </c>
       <c r="D368" s="7"/>
-      <c r="E368" s="7"/>
-      <c r="F368" s="7"/>
-      <c r="G368" s="8"/>
-      <c r="H368" s="8"/>
-      <c r="I368" s="7"/>
-      <c r="J368" s="7"/>
+      <c t="s" r="E368" s="7">
+        <v>419</v>
+      </c>
+      <c r="F368" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G368" s="8">
+        <v>65</v>
+      </c>
+      <c t="s" r="H368" s="8">
+        <v>99</v>
+      </c>
+      <c t="s" r="I368" s="7">
+        <v>420</v>
+      </c>
+      <c t="s" r="J368" s="7">
+        <v>206</v>
+      </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
+      <c t="s" r="M368" s="7">
+        <v>321</v>
+      </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>835</v>
+        <v>730</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>312</v>
+        <v>121</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13090,29 +13208,29 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H370" s="8">
         <v>99</v>
       </c>
-      <c t="s" r="H370" s="8">
-        <v>37</v>
-      </c>
       <c t="s" r="I370" s="7">
-        <v>325</v>
+        <v>395</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13123,29 +13241,29 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>731</v>
+        <v>601</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>381</v>
+        <v>41</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>58</v>
+        <v>275</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13156,29 +13274,29 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H372" s="8">
         <v>99</v>
       </c>
-      <c t="s" r="H372" s="8">
-        <v>24</v>
-      </c>
       <c t="s" r="I372" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13189,145 +13307,145 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>600</v>
+        <v>834</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>43</v>
+        <v>421</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>167</v>
+        <v>422</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c t="s" r="A374" s="6">
-        <v>13</v>
-      </c>
-      <c r="B374" s="7">
-        <v>834</v>
-      </c>
-      <c t="s" r="C374" s="7">
-        <v>14</v>
-      </c>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
       <c r="D374" s="7"/>
-      <c t="s" r="E374" s="7">
-        <v>402</v>
-      </c>
-      <c r="F374" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G374" s="8">
-        <v>99</v>
-      </c>
-      <c t="s" r="H374" s="8">
-        <v>65</v>
-      </c>
-      <c t="s" r="I374" s="7">
-        <v>404</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>405</v>
-      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="7"/>
+      <c r="G374" s="8"/>
+      <c r="H374" s="8"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7"/>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
     </row>
     <row r="375" ht="15" customHeight="1">
-      <c r="A375" s="6"/>
-      <c r="B375" s="7"/>
-      <c r="C375" s="7"/>
+      <c t="s" r="A375" s="6">
+        <v>13</v>
+      </c>
+      <c r="B375" s="7">
+        <v>981</v>
+      </c>
+      <c t="s" r="C375" s="7">
+        <v>14</v>
+      </c>
       <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
-      <c r="F375" s="7"/>
-      <c r="G375" s="8"/>
-      <c r="H375" s="8"/>
-      <c r="I375" s="7"/>
-      <c r="J375" s="7"/>
+      <c t="s" r="E375" s="7">
+        <v>423</v>
+      </c>
+      <c r="F375" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G375" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H375" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I375" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J375" s="7">
+        <v>246</v>
+      </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
-      <c r="M375" s="7"/>
+      <c t="s" r="M375" s="7">
+        <v>68</v>
+      </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
       <c t="s" r="A376" s="6">
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>981</v>
+        <v>946</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>17</v>
+        <v>424</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>209</v>
+        <v>402</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
-      <c t="s" r="M376" s="7">
-        <v>68</v>
-      </c>
+      <c r="M376" s="7"/>
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
+        <v>424</v>
+      </c>
+      <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H377" s="8">
-        <v>407</v>
-      </c>
       <c t="s" r="I377" s="7">
-        <v>388</v>
+        <v>146</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13338,29 +13456,29 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>947</v>
+        <v>491</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>407</v>
+        <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13371,78 +13489,78 @@
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
+        <v>124</v>
+      </c>
+      <c t="s" r="H379" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H379" s="8">
-        <v>124</v>
-      </c>
       <c t="s" r="I379" s="7">
-        <v>126</v>
+        <v>290</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c t="s" r="A380" s="6">
-        <v>13</v>
-      </c>
-      <c r="B380" s="7">
-        <v>492</v>
-      </c>
-      <c t="s" r="C380" s="7">
-        <v>14</v>
-      </c>
+      <c r="A380" s="6"/>
+      <c r="B380" s="7"/>
+      <c r="C380" s="7"/>
       <c r="D380" s="7"/>
-      <c t="s" r="E380" s="7">
-        <v>406</v>
-      </c>
-      <c r="F380" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G380" s="8">
-        <v>124</v>
-      </c>
-      <c t="s" r="H380" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I380" s="7">
-        <v>282</v>
-      </c>
-      <c t="s" r="J380" s="7">
-        <v>169</v>
-      </c>
+      <c r="E380" s="7"/>
+      <c r="F380" s="7"/>
+      <c r="G380" s="8"/>
+      <c r="H380" s="8"/>
+      <c r="I380" s="7"/>
+      <c r="J380" s="7"/>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c r="M380" s="7"/>
     </row>
     <row r="381" ht="14.25" customHeight="1">
-      <c r="A381" s="6"/>
-      <c r="B381" s="7"/>
-      <c r="C381" s="7"/>
+      <c t="s" r="A381" s="6">
+        <v>13</v>
+      </c>
+      <c r="B381" s="7">
+        <v>622</v>
+      </c>
+      <c t="s" r="C381" s="7">
+        <v>14</v>
+      </c>
       <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
-      <c r="F381" s="7"/>
-      <c r="G381" s="8"/>
-      <c r="H381" s="8"/>
-      <c r="I381" s="7"/>
-      <c r="J381" s="7"/>
+      <c t="s" r="E381" s="7">
+        <v>425</v>
+      </c>
+      <c r="F381" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G381" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H381" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I381" s="7">
+        <v>167</v>
+      </c>
+      <c t="s" r="J381" s="7">
+        <v>282</v>
+      </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
@@ -13452,29 +13570,29 @@
         <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>409</v>
+        <v>184</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13507,7 +13625,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13516,10 +13634,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>68</v>
@@ -13527,7 +13645,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13542,13 +13660,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>24</v>
@@ -13575,7 +13693,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13587,10 +13705,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13608,7 +13726,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13617,10 +13735,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>113</v>
@@ -13641,22 +13759,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13689,7 +13807,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13698,17 +13816,19 @@
         <v>24</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>142</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
-      <c r="M390" s="7"/>
+      <c t="s" r="M390" s="7">
+        <v>430</v>
+      </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
       <c t="s" r="A391" s="6">
@@ -13722,13 +13842,13 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>24</v>
@@ -13737,7 +13857,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13755,7 +13875,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13764,13 +13884,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13788,19 +13908,19 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>63</v>
@@ -13836,7 +13956,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13855,7 +13975,9 @@
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
-      <c r="M395" s="7"/>
+      <c t="s" r="M395" s="7">
+        <v>433</v>
+      </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
       <c t="s" r="A396" s="6">
@@ -13869,7 +13991,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -13898,11 +14020,11 @@
         <v>6851</v>
       </c>
       <c t="s" r="C397" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -13911,13 +14033,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13931,23 +14053,23 @@
         <v>6852</v>
       </c>
       <c t="s" r="C398" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>139</v>
@@ -13983,7 +14105,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13992,18 +14114,18 @@
         <v>99</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>420</v>
+        <v>438</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14018,13 +14140,13 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>99</v>
@@ -14033,7 +14155,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14066,13 +14188,13 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>24</v>
@@ -14081,12 +14203,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14101,7 +14223,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14110,13 +14232,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14149,7 +14271,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14164,12 +14286,12 @@
         <v>118</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>424</v>
+        <v>442</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14184,7 +14306,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -14193,17 +14315,19 @@
         <v>99</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
-      <c r="M407" s="7"/>
+      <c t="s" r="M407" s="7">
+        <v>444</v>
+      </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
       <c t="s" r="A408" s="6">
@@ -14217,13 +14341,13 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>99</v>
@@ -14232,7 +14356,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14265,19 +14389,19 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>22</v>
@@ -14285,7 +14409,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>428</v>
+        <v>447</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14300,7 +14424,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14312,10 +14436,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14348,7 +14472,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14360,7 +14484,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>129</v>
@@ -14368,7 +14492,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>430</v>
+        <v>449</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14383,7 +14507,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14395,7 +14519,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>97</v>
@@ -14416,7 +14540,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14428,10 +14552,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14449,7 +14573,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14461,10 +14585,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14482,7 +14606,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14515,7 +14639,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14530,7 +14654,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14563,7 +14687,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14578,12 +14702,12 @@
         <v>139</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14598,7 +14722,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14613,11 +14737,13 @@
         <v>129</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
-      <c r="M421" s="7"/>
+      <c t="s" r="M421" s="7">
+        <v>56</v>
+      </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
       <c t="s" r="A422" s="6">
@@ -14631,7 +14757,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14640,13 +14766,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14664,19 +14790,19 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>118</v>
@@ -14712,7 +14838,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -14721,17 +14847,19 @@
         <v>24</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
-      <c r="M425" s="7"/>
+      <c t="s" r="M425" s="7">
+        <v>454</v>
+      </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
       <c t="s" r="A426" s="6">
@@ -14745,13 +14873,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>24</v>
@@ -14760,7 +14888,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14768,7 +14896,7 @@
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c t="s" r="A427" s="9">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
@@ -14788,7 +14916,7 @@
     <row r="428" ht="65.25" customHeight="1"/>
     <row r="429" ht="16.5" customHeight="1">
       <c t="s" r="A429" s="10">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B429" s="10"/>
       <c r="C429" s="10"/>
@@ -14801,7 +14929,7 @@
       <c r="J429" s="10"/>
       <c r="K429" s="10"/>
       <c t="s" r="L429" s="11">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="M429" s="11"/>
       <c r="N429" s="11"/>
